--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_350_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_350_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7106</v>
+        <v>2.9642</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6063</v>
+        <v>2.414</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1043</v>
+        <v>0.5502</v>
       </c>
       <c r="G2" t="n">
-        <v>0.125</v>
+        <v>1.0953</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3637</v>
+        <v>-0.8488</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4886</v>
+        <v>1.9441</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7829</v>
+        <v>1.9105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7093</v>
+        <v>0.696</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0736</v>
+        <v>1.2146</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.658</v>
+        <v>-0.8152</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.073</v>
+        <v>-1.5448</v>
       </c>
       <c r="O2" t="n">
-        <v>0.415</v>
+        <v>0.7296</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8692</v>
+        <v>0.7813</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7512</v>
+        <v>0.5034</v>
       </c>
       <c r="U2" t="n">
-        <v>1.118</v>
+        <v>0.2779</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7886</v>
+        <v>-0.5361</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8301</v>
+        <v>2.8408</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2463</v>
+        <v>2.2406</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5838</v>
+        <v>0.6002</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0953</v>
+        <v>0.125</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8488</v>
+        <v>-0.3637</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9441</v>
+        <v>0.4886</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9105</v>
+        <v>0.7829</v>
       </c>
       <c r="K3" t="n">
-        <v>0.696</v>
+        <v>0.7093</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2146</v>
+        <v>0.0736</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8152</v>
+        <v>-0.658</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5448</v>
+        <v>-1.073</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7296</v>
+        <v>0.415</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3528</v>
+        <v>0.9994</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6642</v>
+        <v>0.3855</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3115</v>
+        <v>0.6139</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5361</v>
+        <v>0.7886</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8008</v>
+        <v>2.0736</v>
       </c>
       <c r="E4" t="n">
-        <v>2.543</v>
+        <v>2.1773</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7422</v>
+        <v>-0.1037</v>
       </c>
       <c r="G4" t="n">
         <v>3.8762</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0997</v>
+        <v>0.3725</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2467</v>
+        <v>0.881</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.147</v>
+        <v>-0.5085</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8582</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9512</v>
+        <v>-1.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.093</v>
+        <v>0.6561</v>
       </c>
       <c r="G5" t="n">
         <v>-1.53</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0609</v>
+        <v>1.2452</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>0.5192</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1628</v>
+        <v>0.726</v>
       </c>
       <c r="V5" t="n">
         <v>1.4665</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2888</v>
+        <v>-0.7164</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2921</v>
+        <v>-0.8517</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0033</v>
+        <v>0.1353</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.559</v>
+        <v>-1.9961</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5055</v>
+        <v>-1.8355</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0535</v>
+        <v>-0.1605</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0013</v>
+        <v>-1.4887</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.0013</v>
+        <v>-1.4887</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5577</v>
+        <v>-0.5074</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5041</v>
+        <v>-0.3469</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-0.1605</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7341</v>
+        <v>1.0477</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8689</v>
+        <v>0.637</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1349</v>
+        <v>0.4107</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3898</v>
+        <v>-1.1774</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3235</v>
+        <v>-0.1359</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0664</v>
+        <v>-1.0415</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9961</v>
+        <v>-1.4606</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8355</v>
+        <v>-0.5473</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1605</v>
+        <v>-0.9133</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4887</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4887</v>
+        <v>-0.1141</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5074</v>
+        <v>-1.3833</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3469</v>
+        <v>-0.4331</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3743</v>
+        <v>-0.3224</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1652</v>
+        <v>-0.2003</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2091</v>
+        <v>-0.1221</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5827</v>
+        <v>-1.2552</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8762</v>
+        <v>-1.2921</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4589</v>
+        <v>0.0369</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8869</v>
+        <v>-1.559</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3577</v>
+        <v>-1.5055</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2446</v>
+        <v>-0.0535</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1814</v>
+        <v>-1.0013</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1078</v>
+        <v>-1.0013</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0736</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0683</v>
+        <v>-0.5577</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2499</v>
+        <v>-0.5041</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3182</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2889</v>
+        <v>0.7677</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6948</v>
+        <v>0.8689</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4059</v>
+        <v>-0.1013</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6492</v>
+        <v>-1.606</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6077</v>
+        <v>-1.1372</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0415</v>
+        <v>-0.4688</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4606</v>
+        <v>-6.3221</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5473</v>
+        <v>-4.4885</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9133</v>
+        <v>-1.8336</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-4.0882</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1141</v>
+        <v>-2.9437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>-1.1445</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3833</v>
+        <v>-2.2339</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4331</v>
+        <v>-1.5448</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.6891</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7943</v>
+        <v>0.3372</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>0.358</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1221</v>
+        <v>-0.0209</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1418</v>
+        <v>4.147</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>3.7527</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3012</v>
+        <v>-2.1415</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5972</v>
+        <v>-0.4549</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.704</v>
+        <v>-1.6866</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.3221</v>
+        <v>-2.6359</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4885</v>
+        <v>-0.4778</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8336</v>
+        <v>-2.1581</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.0882</v>
+        <v>-0.4671</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9437</v>
+        <v>-0.4671</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1445</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2339</v>
+        <v>-2.1688</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5448</v>
+        <v>-0.0108</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6891</v>
+        <v>-2.1581</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.358</v>
+        <v>-0.2014</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1019</v>
+        <v>-0.1296</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2561</v>
+        <v>-0.0718</v>
       </c>
       <c r="V10" t="n">
-        <v>4.147</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7527</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4183</v>
+        <v>-2.4439</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5702</v>
+        <v>-0.5302</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8481</v>
+        <v>-1.9137</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0827</v>
+        <v>-3.0237</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5403</v>
+        <v>1.7946</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5424</v>
+        <v>-4.8183</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4604</v>
+        <v>-1.4404</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4972</v>
+        <v>1.9024</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>-3.3428</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6223</v>
+        <v>-1.5833</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0431</v>
+        <v>-0.1078</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5792</v>
+        <v>-1.4755</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.2034</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0499</v>
+        <v>-0.0745</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4577</v>
+        <v>0.2779</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4782</v>
+        <v>-2.671</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6908</v>
+        <v>0.6534</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7874</v>
+        <v>-3.3245</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6359</v>
+        <v>-0.8869</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4778</v>
+        <v>0.3577</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1581</v>
+        <v>-1.2446</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4671</v>
+        <v>0.1814</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4671</v>
+        <v>0.1078</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0736</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1688</v>
+        <v>-1.0683</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0108</v>
+        <v>0.2499</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1581</v>
+        <v>-1.3182</v>
       </c>
       <c r="P12" t="n">
         <v>0.6959</v>
@@ -1390,28 +1390,28 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5381</v>
+        <v>0.2005</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3655</v>
+        <v>0.472</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1726</v>
+        <v>-0.2715</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7312</v>
+        <v>-3.4292</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.12</v>
+        <v>-1.5138</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6112</v>
+        <v>-1.9154</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0237</v>
+        <v>-2.0827</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7946</v>
+        <v>-0.5403</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.8183</v>
+        <v>-1.5424</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4404</v>
+        <v>-0.4604</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9024</v>
+        <v>-0.4972</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3428</v>
+        <v>0.0368</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5833</v>
+        <v>-1.6223</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1078</v>
+        <v>-0.0431</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4755</v>
+        <v>-1.5792</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0839</v>
+        <v>-0.4187</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6642</v>
+        <v>0.1063</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5803</v>
+        <v>-0.525</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.3561</v>
+        <v>-8.235900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8808999999999999</v>
+        <v>0.2394999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.475300000000001</v>
+        <v>-8.4755</v>
       </c>
       <c r="G14" t="n">
         <v>-16.4005</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.915400000000001</v>
+        <v>-6.915399999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.485099999999999</v>
+        <v>-9.485100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7276999999999998</v>
+        <v>-0.7276999999999989</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1339</v>
+        <v>2.133899999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.8615</v>
+        <v>-2.861500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-15.6729</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.049200000000001</v>
+        <v>-9.049199999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.6236</v>
+        <v>-6.623600000000001</v>
       </c>
       <c r="P14" t="n">
         <v>-2.3193</v>
@@ -1546,13 +1546,13 @@
         <v>10.4381</v>
       </c>
       <c r="S14" t="n">
-        <v>3.892199999999999</v>
+        <v>5.0124</v>
       </c>
       <c r="T14" t="n">
-        <v>3.206899999999999</v>
+        <v>4.3269</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6854000000000001</v>
+        <v>0.6852999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>5.4717</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>14.3102</v>
+        <v>12.6272</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2099</v>
+        <v>10.2663</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1003</v>
+        <v>2.361</v>
       </c>
       <c r="G15" t="n">
         <v>9.306699999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7896</v>
+        <v>1.1066</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5375</v>
+        <v>0.5939</v>
       </c>
       <c r="U15" t="n">
-        <v>1.252</v>
+        <v>0.5127</v>
       </c>
       <c r="V15" t="n">
         <v>1.7501</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4879</v>
+        <v>3.0371</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0588</v>
+        <v>2.8229</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5709</v>
+        <v>0.2141</v>
       </c>
       <c r="G16" t="n">
         <v>1.7976</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2195</v>
+        <v>-0.6704</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>-0.2711</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1843</v>
+        <v>-0.3993</v>
       </c>
       <c r="V16" t="n">
         <v>1.214</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1032</v>
+        <v>1.8736</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2363</v>
+        <v>2.1183</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1331</v>
+        <v>-0.2447</v>
       </c>
       <c r="G17" t="n">
         <v>1.9632</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0378</v>
+        <v>-0.2673</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0721</v>
+        <v>-0.0395</v>
       </c>
       <c r="V17" t="n">
         <v>-1.214</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8038</v>
+        <v>0.9598</v>
       </c>
       <c r="E18" t="n">
-        <v>1.244</v>
+        <v>1.2847</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4402</v>
+        <v>-0.3249</v>
       </c>
       <c r="G18" t="n">
-        <v>2.435</v>
+        <v>-0.2306</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9293</v>
+        <v>-0.826</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5056</v>
+        <v>0.5954</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9805</v>
+        <v>1.3394</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0504</v>
+        <v>0.9515</v>
       </c>
       <c r="L18" t="n">
-        <v>0.93</v>
+        <v>0.3879</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4545</v>
+        <v>-1.57</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8789</v>
+        <v>-1.7775</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5756</v>
+        <v>0.2075</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4867</v>
+        <v>-0.0569</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>-0.0547</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7503</v>
+        <v>-0.0022</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6732</v>
+        <v>0.8482</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.7722</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2577</v>
+        <v>0.076</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2306</v>
+        <v>2.435</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.826</v>
+        <v>0.9293</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5954</v>
+        <v>1.5056</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3394</v>
+        <v>0.9805</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9515</v>
+        <v>0.0504</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3879</v>
+        <v>0.93</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.57</v>
+        <v>1.4545</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7775</v>
+        <v>0.8789</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2075</v>
+        <v>0.5756</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3435</v>
+        <v>-0.4424</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4086</v>
+        <v>-0.2082</v>
       </c>
       <c r="U19" t="n">
-        <v>0.065</v>
+        <v>-0.2341</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9066</v>
+        <v>0.1867</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1851</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2784</v>
+        <v>-0.4983</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0809</v>
+        <v>-0.0387</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3218</v>
+        <v>1.3901</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2409</v>
+        <v>-1.4287</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6623</v>
+        <v>1.1023</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0504</v>
+        <v>2.5277</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>-1.4255</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7432</v>
+        <v>-1.1409</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2714</v>
+        <v>-1.1377</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4718</v>
+        <v>-0.0033</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2195</v>
+        <v>-0.5375</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>-0.1647</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6967</v>
+        <v>-0.3727</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.3247</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1445</v>
+        <v>-0.497</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0887</v>
+        <v>-1.0671</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2332</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4156</v>
+        <v>0.0809</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1345</v>
+        <v>0.3218</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2811</v>
+        <v>-0.2409</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9558</v>
+        <v>-0.6623</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8822</v>
+        <v>0.0504</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5401</v>
+        <v>0.7432</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7477</v>
+        <v>0.2714</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2075</v>
+        <v>0.4718</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2955</v>
+        <v>-0.8098</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6122</v>
+        <v>-0.4048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3167</v>
+        <v>-0.405</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1935</v>
+        <v>-1.0527</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7636</v>
+        <v>-1.6457</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5929</v>
       </c>
       <c r="G22" t="n">
         <v>1.7805</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2759</v>
+        <v>0.4167</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0395</v>
+        <v>0.1575</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2364</v>
+        <v>0.2592</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9304</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2953</v>
+        <v>-1.9607</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4945</v>
+        <v>-2.5244</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8008</v>
+        <v>0.5636</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0387</v>
+        <v>2.0358</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3901</v>
+        <v>0.838</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4287</v>
+        <v>1.1977</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1023</v>
+        <v>0.424</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5277</v>
+        <v>-0.1982</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4255</v>
+        <v>0.6222</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1409</v>
+        <v>1.6118</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1377</v>
+        <v>1.0362</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0033</v>
+        <v>0.5756</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0876</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0195</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3443</v>
+        <v>-0.6289</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6752</v>
+        <v>-0.2981</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3247</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4268</v>
+        <v>-2.4527</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6423</v>
+        <v>-1.2087</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2155</v>
+        <v>-1.244</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0358</v>
+        <v>1.4156</v>
       </c>
       <c r="H24" t="n">
-        <v>0.838</v>
+        <v>1.1345</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1977</v>
+        <v>0.2811</v>
       </c>
       <c r="J24" t="n">
-        <v>0.424</v>
+        <v>1.9558</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1982</v>
+        <v>1.8822</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6222</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6118</v>
+        <v>-0.5401</v>
       </c>
       <c r="N24" t="n">
-        <v>1.0362</v>
+        <v>-0.7477</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5756</v>
+        <v>0.2075</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8556</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.393</v>
+        <v>-0.0127</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7468</v>
+        <v>0.3148</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6462</v>
+        <v>-0.3275</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0554</v>
+        <v>-2.6406</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2077</v>
+        <v>-3.0282</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1523</v>
+        <v>0.3876</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1455</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5336</v>
+        <v>-0.1188</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9709</v>
+        <v>0.2087</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5627</v>
+        <v>-0.3275</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.356199999999998</v>
+        <v>10.9289</v>
       </c>
       <c r="E26" t="n">
-        <v>8.475399999999997</v>
+        <v>8.475300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8806999999999999</v>
+        <v>2.4534</v>
       </c>
       <c r="G26" t="n">
         <v>16.4005</v>
@@ -2461,10 +2461,10 @@
         <v>9.049199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>6.623700000000001</v>
+        <v>6.623699999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7275999999999992</v>
+        <v>0.7275999999999995</v>
       </c>
       <c r="N26" t="n">
         <v>-2.134</v>
@@ -2473,7 +2473,7 @@
         <v>2.8615</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3197</v>
+        <v>2.319699999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-10.4379</v>
@@ -2482,13 +2482,13 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.8921</v>
+        <v>-2.3194</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6855</v>
+        <v>-0.6853000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.2066</v>
+        <v>-1.634</v>
       </c>
       <c r="V26" t="n">
         <v>-5.4717</v>
